--- a/Pb210_spreadsheet_example_GC-03.xlsx
+++ b/Pb210_spreadsheet_example_GC-03.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\riley\Documents\Github\Pb210Modeler\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77F0E88F-9CA3-4E61-AA27-A158A4AF7BE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7FBE9DAD-0E4E-4719-A511-249084965933}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Constants" sheetId="15" r:id="rId1"/>
@@ -3156,7 +3156,7 @@
     <xf numFmtId="0" fontId="43" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="341">
+  <cellXfs count="342">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3988,10 +3988,13 @@
     <xf numFmtId="169" fontId="4" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="1" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="1" xfId="0" applyFont="1"/>
+    <xf numFmtId="171" fontId="4" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="353">
     <cellStyle name="Followed Hyperlink" xfId="236" builtinId="9" hidden="1"/>
@@ -19182,14 +19185,14 @@
         </a:ln>
         <a:extLst>
           <a:ext uri="{909E8E84-426E-40dd-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns="" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns="">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
             </a14:hiddenFill>
           </a:ext>
           <a:ext uri="{91240B29-F687-4f45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns="" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns="" w="9525">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
@@ -19947,14 +19950,14 @@
         </a:ln>
         <a:extLst>
           <a:ext uri="{909E8E84-426E-40dd-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns="" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns="">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
             </a14:hiddenFill>
           </a:ext>
           <a:ext uri="{91240B29-F687-4f45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns="" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns="" w="9525">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
@@ -20009,14 +20012,14 @@
         <a:effectLst/>
         <a:extLst>
           <a:ext uri="{909E8E84-426E-40dd-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns="" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns="">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
             </a14:hiddenFill>
           </a:ext>
           <a:ext uri="{91240B29-F687-4f45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns="" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns="" w="9525">
               <a:solidFill>
                 <a:schemeClr val="tx1"/>
               </a:solidFill>
@@ -20026,7 +20029,7 @@
             </a14:hiddenLine>
           </a:ext>
           <a:ext uri="{AF507438-7753-43e0-B8FC-AC1667EBCBE1}">
-            <a14:hiddenEffects xmlns="" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+            <a14:hiddenEffects xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns="">
               <a:effectLst>
                 <a:outerShdw blurRad="63500" dist="38099" dir="2700000" algn="ctr" rotWithShape="0">
                   <a:schemeClr val="bg2">
@@ -20273,14 +20276,14 @@
         <a:effectLst/>
         <a:extLst>
           <a:ext uri="{909E8E84-426E-40dd-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns="" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns="">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
             </a14:hiddenFill>
           </a:ext>
           <a:ext uri="{91240B29-F687-4f45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns="" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns="" w="9525">
               <a:solidFill>
                 <a:schemeClr val="tx1"/>
               </a:solidFill>
@@ -20290,7 +20293,7 @@
             </a14:hiddenLine>
           </a:ext>
           <a:ext uri="{AF507438-7753-43e0-B8FC-AC1667EBCBE1}">
-            <a14:hiddenEffects xmlns="" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+            <a14:hiddenEffects xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns="">
               <a:effectLst>
                 <a:outerShdw blurRad="63500" dist="38099" dir="2700000" algn="ctr" rotWithShape="0">
                   <a:schemeClr val="bg2">
@@ -20563,14 +20566,14 @@
         <a:effectLst/>
         <a:extLst>
           <a:ext uri="{909E8E84-426E-40dd-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns="" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns="">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
             </a14:hiddenFill>
           </a:ext>
           <a:ext uri="{91240B29-F687-4f45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns="" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns="" w="9525">
               <a:solidFill>
                 <a:schemeClr val="tx1"/>
               </a:solidFill>
@@ -20580,7 +20583,7 @@
             </a14:hiddenLine>
           </a:ext>
           <a:ext uri="{AF507438-7753-43e0-B8FC-AC1667EBCBE1}">
-            <a14:hiddenEffects xmlns="" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+            <a14:hiddenEffects xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns="">
               <a:effectLst>
                 <a:outerShdw blurRad="63500" dist="38099" dir="2700000" algn="ctr" rotWithShape="0">
                   <a:schemeClr val="bg2">
@@ -21838,7 +21841,7 @@
       <c r="A3" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="340" t="s">
+      <c r="B3" s="339" t="s">
         <v>272</v>
       </c>
       <c r="D3" s="29"/>
@@ -34648,11 +34651,11 @@
       <c r="P2" s="169" t="s">
         <v>104</v>
       </c>
-      <c r="Q2" s="339" t="s">
+      <c r="Q2" s="340" t="s">
         <v>40</v>
       </c>
-      <c r="R2" s="339"/>
-      <c r="S2" s="339"/>
+      <c r="R2" s="340"/>
+      <c r="S2" s="340"/>
       <c r="AI2" s="23" t="s">
         <v>105</v>
       </c>
@@ -41647,7 +41650,7 @@
     <col min="7" max="8" width="7" style="45" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13" style="19" customWidth="1"/>
     <col min="10" max="10" width="10.54296875" style="24" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.453125" style="24" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.1796875" style="24" customWidth="1"/>
     <col min="12" max="12" width="11" style="19" customWidth="1"/>
     <col min="13" max="14" width="8.36328125" style="24" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="10.81640625" style="24" bestFit="1" customWidth="1"/>
@@ -41898,9 +41901,9 @@
         <f>Constants!$B$25*CF!E6/Concentrations!I4</f>
         <v>0.11238917447365696</v>
       </c>
-      <c r="K6" s="261">
-        <f>J6*SQRT(SUMSQ(Constants!$B$26/Constants!$B$25,CF!F6/CF!E6,Concentrations!J4/Concentrations!I4))</f>
-        <v>8.7459062426716635E-3</v>
+      <c r="K6" s="341">
+        <f>J6*SQRT((F6/E6)^2+(1-(E6-E8)/(E6))*(Concentrations!J4/Concentrations!I4)^2)</f>
+        <v>8.4843514027324856E-3</v>
       </c>
       <c r="L6" s="306"/>
       <c r="M6" s="307"/>
@@ -41918,7 +41921,7 @@
       </c>
       <c r="Q6" s="152">
         <f>P6*SQRT(SUMSQ(K6/J6,O6/N6))</f>
-        <v>6.0192086815780942E-2</v>
+        <v>5.9422287048864528E-2</v>
       </c>
       <c r="T6" s="24">
         <f>J6*10000</f>
@@ -41964,7 +41967,7 @@
       <c r="H7" s="24"/>
       <c r="I7" s="81"/>
       <c r="J7" s="152"/>
-      <c r="K7" s="261"/>
+      <c r="K7" s="341"/>
       <c r="L7" s="308">
         <f>Masses!E8</f>
         <v>0.2261039229</v>
@@ -42016,9 +42019,9 @@
         <f>Constants!$B$25*CF!E8/Concentrations!I6</f>
         <v>0.12636293273444277</v>
       </c>
-      <c r="K8" s="261">
-        <f>J8*SQRT(SUMSQ(Constants!$B$26/Constants!$B$25,CF!F8/CF!E8,Concentrations!J6/Concentrations!I6))</f>
-        <v>1.3225345005936507E-3</v>
+      <c r="K8" s="341">
+        <f>J8*SQRT((F8/E8)^2+(1-(E8-E10)/(E8))*(Concentrations!J6/Concentrations!I6)^2)</f>
+        <v>1.112210323231074E-3</v>
       </c>
       <c r="L8" s="306"/>
       <c r="M8" s="305"/>
@@ -42036,7 +42039,7 @@
       </c>
       <c r="Q8" s="152">
         <f>P8*SQRT(SUMSQ(K8/J8,O8/N8))</f>
-        <v>8.4083549233317009E-3</v>
+        <v>7.9077786633262766E-3</v>
       </c>
       <c r="T8" s="24">
         <f>J8*10000</f>
@@ -42085,7 +42088,7 @@
       <c r="H9" s="24"/>
       <c r="I9" s="81"/>
       <c r="J9" s="152"/>
-      <c r="K9" s="261"/>
+      <c r="K9" s="341"/>
       <c r="L9" s="308">
         <f>Masses!E10</f>
         <v>0.27468829319999999</v>
@@ -42142,9 +42145,9 @@
         <f>Constants!$B$25*CF!E10/Concentrations!I8</f>
         <v>0.11610050031352451</v>
       </c>
-      <c r="K10" s="261">
-        <f>J10*SQRT(SUMSQ(Constants!$B$26/Constants!$B$25,CF!F10/CF!E10,Concentrations!J8/Concentrations!I8))</f>
-        <v>1.2258527970489925E-3</v>
+      <c r="K10" s="341">
+        <f>J10*SQRT((F10/E10)^2+(1-(E10-E12)/(E10))*(Concentrations!J8/Concentrations!I8)^2)</f>
+        <v>1.0309836459693889E-3</v>
       </c>
       <c r="L10" s="306"/>
       <c r="M10" s="305"/>
@@ -42162,7 +42165,7 @@
       </c>
       <c r="Q10" s="152">
         <f>P10*SQRT(SUMSQ(K10/J10,O10/N10))</f>
-        <v>6.4333514655289855E-3</v>
+        <v>5.9799428626076036E-3</v>
       </c>
       <c r="T10" s="24">
         <f>J10*10000</f>
@@ -42212,7 +42215,7 @@
       <c r="H11" s="24"/>
       <c r="I11" s="81"/>
       <c r="J11" s="152"/>
-      <c r="K11" s="261"/>
+      <c r="K11" s="341"/>
       <c r="L11" s="308">
         <f>Masses!E12</f>
         <v>0.28437783509999998</v>
@@ -42267,9 +42270,9 @@
         <f>Constants!$B$25*CF!E12/Concentrations!I10</f>
         <v>0.10424178776252202</v>
       </c>
-      <c r="K12" s="261">
-        <f>J12*SQRT(SUMSQ(Constants!$B$26/Constants!$B$25,CF!F12/CF!E12,Concentrations!J10/Concentrations!I10))</f>
-        <v>1.1127286034891305E-3</v>
+      <c r="K12" s="341">
+        <f>J12*SQRT((F12/E12)^2+(1-(E12-E14)/(E12))*(Concentrations!J10/Concentrations!I10)^2)</f>
+        <v>9.3986398939817405E-4</v>
       </c>
       <c r="L12" s="306"/>
       <c r="M12" s="305"/>
@@ -42287,7 +42290,7 @@
       </c>
       <c r="Q12" s="152">
         <f>P12*SQRT(SUMSQ(K12/J12,O12/N12))</f>
-        <v>5.6479006438826147E-3</v>
+        <v>5.2565962573102145E-3</v>
       </c>
       <c r="T12" s="24">
         <f>J12*10000</f>
@@ -42334,7 +42337,7 @@
       <c r="H13" s="24"/>
       <c r="I13" s="81"/>
       <c r="J13" s="152"/>
-      <c r="K13" s="261"/>
+      <c r="K13" s="341"/>
       <c r="L13" s="308">
         <f>Masses!E14</f>
         <v>0.29235443179999998</v>
@@ -42388,9 +42391,9 @@
         <f>Constants!$B$25*CF!E14/Concentrations!I12</f>
         <v>9.9137865653838017E-2</v>
       </c>
-      <c r="K14" s="261">
-        <f>J14*SQRT(SUMSQ(Constants!$B$26/Constants!$B$25,CF!F26/CF!E26,Concentrations!J12/Concentrations!I12))</f>
-        <v>1.3383989820854171E-3</v>
+      <c r="K14" s="341">
+        <f>J14*SQRT((F14/E14)^2+(1-(E14-E16)/(E14))*(Concentrations!J12/Concentrations!I12)^2)</f>
+        <v>9.3792777027984313E-4</v>
       </c>
       <c r="L14" s="306"/>
       <c r="M14" s="305"/>
@@ -42408,7 +42411,7 @@
       </c>
       <c r="Q14" s="152">
         <f>P14*SQRT(SUMSQ(K14/J14,O14/N14))</f>
-        <v>5.9146364078230193E-3</v>
+        <v>4.9432202242780674E-3</v>
       </c>
       <c r="T14" s="24">
         <f>J14*10000</f>
@@ -42452,7 +42455,7 @@
       <c r="H15" s="24"/>
       <c r="I15" s="81"/>
       <c r="J15" s="152"/>
-      <c r="K15" s="261"/>
+      <c r="K15" s="341"/>
       <c r="L15" s="308">
         <f>Masses!E16</f>
         <v>0.29561971310000001</v>
@@ -42509,9 +42512,9 @@
         <f>Constants!$B$25*CF!E16/Concentrations!I14</f>
         <v>9.4897011000103393E-2</v>
       </c>
-      <c r="K16" s="261">
-        <f>J16*SQRT(SUMSQ(Constants!$B$26/Constants!$B$25,CF!F28/CF!E28,Concentrations!J14/Concentrations!I14))</f>
-        <v>1.3480611150380514E-3</v>
+      <c r="K16" s="341">
+        <f>J16*SQRT((F16/E16)^2+(1-(E16-E18)/(E16))*(Concentrations!J14/Concentrations!I14)^2)</f>
+        <v>9.5349797109918835E-4</v>
       </c>
       <c r="L16" s="306"/>
       <c r="M16" s="305"/>
@@ -42529,7 +42532,7 @@
       </c>
       <c r="Q16" s="152">
         <f>P16*SQRT(SUMSQ(K16/J16,O16/N16))</f>
-        <v>5.8281386808484983E-3</v>
+        <v>4.8523339491882058E-3</v>
       </c>
       <c r="T16" s="24">
         <f>J16*10000</f>
@@ -42573,7 +42576,7 @@
       <c r="H17" s="24"/>
       <c r="I17" s="81"/>
       <c r="J17" s="152"/>
-      <c r="K17" s="261"/>
+      <c r="K17" s="341"/>
       <c r="L17" s="308">
         <f>Masses!E18</f>
         <v>0.2947480327</v>
@@ -42630,9 +42633,9 @@
         <f>Constants!$B$25*CF!E18/Concentrations!I16</f>
         <v>9.0620193574578387E-2</v>
       </c>
-      <c r="K18" s="261">
-        <f>J18*SQRT(SUMSQ(Constants!$B$26/Constants!$B$25,CF!F18/CF!E18,Concentrations!J16/Concentrations!I16))</f>
-        <v>1.1031204377831426E-3</v>
+      <c r="K18" s="341">
+        <f>J18*SQRT((F18/E18)^2+(1-(E18-E20)/(E18))*(Concentrations!J16/Concentrations!I16)^2)</f>
+        <v>9.6590315221281272E-4</v>
       </c>
       <c r="L18" s="306"/>
       <c r="M18" s="305"/>
@@ -42650,7 +42653,7 @@
       </c>
       <c r="Q18" s="152">
         <f>P18*SQRT(SUMSQ(K18/J18,O18/N18))</f>
-        <v>5.2304204310881924E-3</v>
+        <v>4.9016206163194354E-3</v>
       </c>
       <c r="T18" s="24">
         <f>J18*10000</f>
@@ -42693,7 +42696,7 @@
       <c r="H19" s="24"/>
       <c r="I19" s="81"/>
       <c r="J19" s="152"/>
-      <c r="K19" s="261"/>
+      <c r="K19" s="341"/>
       <c r="L19" s="308">
         <f>Masses!E20</f>
         <v>0.28910410730000002</v>
@@ -42740,9 +42743,9 @@
         <f>Constants!$B$25*CF!E20/Concentrations!I18</f>
         <v>8.7631386877700126E-2</v>
       </c>
-      <c r="K20" s="261">
-        <f>J20*SQRT(SUMSQ(Constants!$B$26/Constants!$B$25,CF!F20/CF!E20,Concentrations!J18/Concentrations!I18))</f>
-        <v>1.1310782648108907E-3</v>
+      <c r="K20" s="341">
+        <f>J20*SQRT((F20/E20)^2+(1-(E20-E22)/(E20))*(Concentrations!J18/Concentrations!I18)^2)</f>
+        <v>1.0049332064537995E-3</v>
       </c>
       <c r="L20" s="306"/>
       <c r="M20" s="305"/>
@@ -42760,7 +42763,7 @@
       </c>
       <c r="Q20" s="152">
         <f>P20*SQRT(SUMSQ(K20/J20,O20/N20))</f>
-        <v>5.4098390872897506E-3</v>
+        <v>5.0960934172753804E-3</v>
       </c>
       <c r="T20" s="24">
         <f>J20*10000</f>
@@ -42847,8 +42850,8 @@
         <v>9.8891960290145742E-2</v>
       </c>
       <c r="K22" s="261">
-        <f>J22*SQRT(SUMSQ(Constants!$B$26/Constants!$B$25,CF!F22/CF!E22,Concentrations!J20/Concentrations!I20))</f>
-        <v>1.4429809306199821E-3</v>
+        <f>J22*SQRT((F22/E22)^2+(1-(E22-E24)/(E22))*(Concentrations!J20/Concentrations!I20)^2)</f>
+        <v>1.3135444164565785E-3</v>
       </c>
       <c r="L22" s="306"/>
       <c r="M22" s="305"/>
@@ -42866,7 +42869,7 @@
       </c>
       <c r="Q22" s="152">
         <f>P22*SQRT(SUMSQ(K22/J22,O22/N22))</f>
-        <v>6.6440411438817857E-3</v>
+        <v>6.3001567265097659E-3</v>
       </c>
       <c r="T22" s="24">
         <f>J22*10000</f>
@@ -42953,8 +42956,8 @@
         <v>0.10896992211647455</v>
       </c>
       <c r="K24" s="261">
-        <f>J24*SQRT(SUMSQ(Constants!$B$26/Constants!$B$25,CF!F24/CF!E24,Concentrations!J22/Concentrations!I22))</f>
-        <v>1.7726143551220867E-3</v>
+        <f>J24*SQRT((F24/E24)^2+(1-(E24-E26)/(E24))*(Concentrations!J22/Concentrations!I22)^2)</f>
+        <v>1.6342378620337428E-3</v>
       </c>
       <c r="L24" s="306"/>
       <c r="M24" s="305"/>
@@ -42972,7 +42975,7 @@
       </c>
       <c r="Q24" s="152">
         <f>P24*SQRT(SUMSQ(K24/J24,O24/N24))</f>
-        <v>8.1913178264032046E-3</v>
+        <v>7.797919654217441E-3</v>
       </c>
       <c r="T24" s="24">
         <f>J24*10000</f>
@@ -43070,8 +43073,8 @@
         <v>0.10365539793914934</v>
       </c>
       <c r="K26" s="261">
-        <f>J26*SQRT(SUMSQ(Constants!$B$26/Constants!$B$25,CF!F26/CF!E26,Concentrations!J24/Concentrations!I24))</f>
-        <v>1.7504201466462983E-3</v>
+        <f>J26*SQRT((F26/E26)^2+(1-(E26-E28)/(E26))*(Concentrations!J24/Concentrations!I24)^2)</f>
+        <v>1.620718363257549E-3</v>
       </c>
       <c r="L26" s="306"/>
       <c r="M26" s="305"/>
@@ -43089,7 +43092,7 @@
       </c>
       <c r="Q26" s="152">
         <f>P26*SQRT(SUMSQ(K26/J26,O26/N26))</f>
-        <v>8.2693005800785098E-3</v>
+        <v>7.8886026229016918E-3</v>
       </c>
       <c r="T26" s="24">
         <f>J26*10000</f>
@@ -43177,8 +43180,8 @@
         <v>0.11080380340286598</v>
       </c>
       <c r="K28" s="261">
-        <f>J28*SQRT(SUMSQ(Constants!$B$26/Constants!$B$25,CF!F28/CF!E28,Concentrations!J26/Concentrations!I26))</f>
-        <v>2.0748780815133356E-3</v>
+        <f>J28*SQRT((F28/E28)^2+(1-(E28-E30)/(E28))*(Concentrations!J26/Concentrations!I26)^2)</f>
+        <v>1.9480327938213552E-3</v>
       </c>
       <c r="L28" s="306"/>
       <c r="M28" s="305"/>
@@ -43196,7 +43199,7 @@
       </c>
       <c r="Q28" s="152">
         <f>P28*SQRT(SUMSQ(K28/J28,O28/N28))</f>
-        <v>9.7487142418629796E-3</v>
+        <v>9.3571996550108859E-3</v>
       </c>
       <c r="T28" s="24">
         <f>J28*10000</f>
@@ -43283,8 +43286,8 @@
         <v>0.11884815796281578</v>
       </c>
       <c r="K30" s="261">
-        <f>J30*SQRT(SUMSQ(Constants!$B$26/Constants!$B$25,CF!F30/CF!E30,Concentrations!J28/Concentrations!I28))</f>
-        <v>2.4501306055785426E-3</v>
+        <f>J30*SQRT((F30/E30)^2+(1-(E30-E32)/(E30))*(Concentrations!J28/Concentrations!I28)^2)</f>
+        <v>2.3094497496803272E-3</v>
       </c>
       <c r="L30" s="306"/>
       <c r="M30" s="305"/>
@@ -43302,7 +43305,7 @@
       </c>
       <c r="Q30" s="152">
         <f>P30*SQRT(SUMSQ(K30/J30,O30/N30))</f>
-        <v>1.1210108297514685E-2</v>
+        <v>1.0763595635360291E-2</v>
       </c>
       <c r="T30" s="24">
         <f>J30*10000</f>
@@ -43390,8 +43393,8 @@
         <v>0.10299011276851647</v>
       </c>
       <c r="K32" s="261">
-        <f>J32*SQRT(SUMSQ(Constants!$B$26/Constants!$B$25,CF!F32/CF!E32,Concentrations!J30/Concentrations!I30))</f>
-        <v>2.0784068377782102E-3</v>
+        <f>J32*SQRT((F32/E32)^2+(1-(E32-E34)/(E32))*(Concentrations!J30/Concentrations!I30)^2)</f>
+        <v>1.9496056524568749E-3</v>
       </c>
       <c r="L32" s="306"/>
       <c r="M32" s="305"/>
@@ -43409,7 +43412,7 @@
       </c>
       <c r="Q32" s="152">
         <f>P32*SQRT(SUMSQ(K32/J32,O32/N32))</f>
-        <v>9.0965346951233633E-3</v>
+        <v>8.6949744080141982E-3</v>
       </c>
       <c r="T32" s="24">
         <f>J32*10000</f>
@@ -43498,8 +43501,8 @@
         <v>8.574309217077361E-2</v>
       </c>
       <c r="K34" s="261">
-        <f>J34*SQRT(SUMSQ(Constants!$B$26/Constants!$B$25,CF!F34/CF!E34,Concentrations!J32/Concentrations!I32))</f>
-        <v>1.7015605422208669E-3</v>
+        <f>J34*SQRT((F34/E34)^2+(1-(E34-E36)/(E34))*(Concentrations!J32/Concentrations!I32)^2)</f>
+        <v>1.5937966948168666E-3</v>
       </c>
       <c r="L34" s="306"/>
       <c r="M34" s="305"/>
@@ -43517,7 +43520,7 @@
       </c>
       <c r="Q34" s="152">
         <f>P34*SQRT(SUMSQ(K34/J34,O34/N34))</f>
-        <v>7.227829530616587E-3</v>
+        <v>6.8880506985852111E-3</v>
       </c>
       <c r="T34" s="24">
         <f>J34*10000</f>
@@ -43604,8 +43607,8 @@
         <v>7.8165185388270081E-2</v>
       </c>
       <c r="K36" s="261">
-        <f>J36*SQRT(SUMSQ(Constants!$B$26/Constants!$B$25,CF!F36/CF!E36,Concentrations!J34/Concentrations!I34))</f>
-        <v>1.6287800091576302E-3</v>
+        <f>J36*SQRT((F36/E36)^2+(1-(E36-E38)/(E36))*(Concentrations!J34/Concentrations!I34)^2)</f>
+        <v>1.5340346963077466E-3</v>
       </c>
       <c r="L36" s="306"/>
       <c r="M36" s="305"/>
@@ -43623,7 +43626,7 @@
       </c>
       <c r="Q36" s="152">
         <f>P36*SQRT(SUMSQ(K36/J36,O36/N36))</f>
-        <v>6.9040907900629707E-3</v>
+        <v>6.6019535616052257E-3</v>
       </c>
       <c r="R36" s="24"/>
       <c r="S36" s="24"/>
@@ -43690,7 +43693,7 @@
       <c r="H37" s="24"/>
       <c r="I37" s="24"/>
       <c r="J37" s="152"/>
-      <c r="K37" s="152"/>
+      <c r="K37" s="261"/>
       <c r="L37" s="308">
         <f>Masses!E38</f>
         <v>0.26741338619999999</v>
@@ -43770,8 +43773,8 @@
         <v>7.8305437868672334E-2</v>
       </c>
       <c r="K38" s="261">
-        <f>J38*SQRT(SUMSQ(Constants!$B$26/Constants!$B$25,CF!F38/CF!E38,Concentrations!J36/Concentrations!I36))</f>
-        <v>1.7917261845719799E-3</v>
+        <f>J38*SQRT((F38/E38)^2+(1-(E38-E40)/(E38))*(Concentrations!J36/Concentrations!I36)^2)</f>
+        <v>1.6983459123945373E-3</v>
       </c>
       <c r="L38" s="125"/>
       <c r="M38" s="24"/>
@@ -43789,7 +43792,7 @@
       </c>
       <c r="Q38" s="152">
         <f t="shared" ref="Q38" si="23">P38*SQRT(SUMSQ(K38/J38,O38/N38))</f>
-        <v>7.6566343890271732E-3</v>
+        <v>7.3561785351594329E-3</v>
       </c>
       <c r="R38" s="24"/>
       <c r="S38" s="24"/>
@@ -43855,7 +43858,7 @@
       <c r="H39" s="24"/>
       <c r="I39" s="24"/>
       <c r="J39" s="152"/>
-      <c r="K39" s="152"/>
+      <c r="K39" s="261"/>
       <c r="L39" s="120">
         <f>Masses!E40</f>
         <v>0.27017934910000002</v>
@@ -43934,8 +43937,8 @@
         <v>8.4789942662707271E-2</v>
       </c>
       <c r="K40" s="261">
-        <f>J40*SQRT(SUMSQ(Constants!$B$26/Constants!$B$25,CF!F40/CF!E40,Concentrations!J38/Concentrations!I38))</f>
-        <v>2.2093190204750075E-3</v>
+        <f>J40*SQRT((F40/E40)^2+(1-(E40-E42)/(E40))*(Concentrations!J38/Concentrations!I38)^2)</f>
+        <v>2.1092544277200973E-3</v>
       </c>
       <c r="L40" s="125"/>
       <c r="M40" s="24"/>
@@ -43953,7 +43956,7 @@
       </c>
       <c r="Q40" s="152">
         <f t="shared" ref="Q40" si="33">P40*SQRT(SUMSQ(K40/J40,O40/N40))</f>
-        <v>9.1505235002697291E-3</v>
+        <v>8.8226870163622372E-3</v>
       </c>
       <c r="R40" s="24"/>
       <c r="S40" s="24"/>
@@ -44019,7 +44022,7 @@
       <c r="H41" s="24"/>
       <c r="I41" s="24"/>
       <c r="J41" s="152"/>
-      <c r="K41" s="152"/>
+      <c r="K41" s="261"/>
       <c r="L41" s="120">
         <f>Masses!E42</f>
         <v>0.27144589120000001</v>
@@ -44099,8 +44102,8 @@
         <v>8.8573664451366718E-2</v>
       </c>
       <c r="K42" s="261">
-        <f>J42*SQRT(SUMSQ(Constants!$B$26/Constants!$B$25,CF!F42/CF!E42,Concentrations!J40/Concentrations!I40))</f>
-        <v>2.5644652719998091E-3</v>
+        <f>J42*SQRT((F42/E42)^2+(1-(E42-E44)/(E42))*(Concentrations!J40/Concentrations!I40)^2)</f>
+        <v>2.4514959933052741E-3</v>
       </c>
       <c r="L42" s="125"/>
       <c r="M42" s="24"/>
@@ -44118,7 +44121,7 @@
       </c>
       <c r="Q42" s="152">
         <f t="shared" ref="Q42" si="43">P42*SQRT(SUMSQ(K42/J42,O42/N42))</f>
-        <v>1.0341143947660798E-2</v>
+        <v>9.9630460623165752E-3</v>
       </c>
       <c r="R42" s="24"/>
       <c r="S42" s="24"/>
@@ -44187,7 +44190,7 @@
       <c r="H43" s="24"/>
       <c r="I43" s="24"/>
       <c r="J43" s="152"/>
-      <c r="K43" s="152"/>
+      <c r="K43" s="261"/>
       <c r="L43" s="120">
         <f>Masses!E44</f>
         <v>0.27191991119999998</v>
@@ -44269,8 +44272,8 @@
         <v>8.231146583212394E-2</v>
       </c>
       <c r="K44" s="261">
-        <f>J44*SQRT(SUMSQ(Constants!$B$26/Constants!$B$25,CF!F44/CF!E44,Concentrations!J42/Concentrations!I42))</f>
-        <v>2.5031527668349231E-3</v>
+        <f>J44*SQRT((F44/E44)^2+(1-(E44-E46)/(E44))*(Concentrations!J42/Concentrations!I42)^2)</f>
+        <v>2.3955427750721749E-3</v>
       </c>
       <c r="L44" s="125"/>
       <c r="M44" s="24"/>
@@ -44288,7 +44291,7 @@
       </c>
       <c r="Q44" s="152">
         <f t="shared" ref="Q44" si="53">P44*SQRT(SUMSQ(K44/J44,O44/N44))</f>
-        <v>1.0042906335339174E-2</v>
+        <v>9.676030855637353E-3</v>
       </c>
       <c r="R44" s="24"/>
       <c r="S44" s="24"/>
@@ -44360,7 +44363,7 @@
       <c r="H45" s="24"/>
       <c r="I45" s="24"/>
       <c r="J45" s="152"/>
-      <c r="K45" s="152"/>
+      <c r="K45" s="261"/>
       <c r="L45" s="120">
         <f>Masses!E46</f>
         <v>0.26795783220000002</v>
@@ -44440,8 +44443,8 @@
         <v>8.6407364388369531E-2</v>
       </c>
       <c r="K46" s="261">
-        <f>J46*SQRT(SUMSQ(Constants!$B$26/Constants!$B$25,CF!F46/CF!E46,Concentrations!J44/Concentrations!I44))</f>
-        <v>2.9701970591999183E-3</v>
+        <f>J46*SQRT((F46/E46)^2+(1-(E46-E48)/(E46))*(Concentrations!J44/Concentrations!I44)^2)</f>
+        <v>2.8495458634539479E-3</v>
       </c>
       <c r="L46" s="125"/>
       <c r="M46" s="24"/>
@@ -44459,7 +44462,7 @@
       </c>
       <c r="Q46" s="152">
         <f t="shared" ref="Q46" si="63">P46*SQRT(SUMSQ(K46/J46,O46/N46))</f>
-        <v>1.0546121049554252E-2</v>
+        <v>1.0161054483039188E-2</v>
       </c>
       <c r="R46" s="24"/>
       <c r="S46" s="24"/>
@@ -44526,7 +44529,7 @@
       <c r="H47" s="24"/>
       <c r="I47" s="24"/>
       <c r="J47" s="152"/>
-      <c r="K47" s="152"/>
+      <c r="K47" s="261"/>
       <c r="L47" s="120">
         <f>Masses!E48</f>
         <v>0.32554032189999998</v>
@@ -44603,8 +44606,8 @@
         <v>9.4478373884883685E-2</v>
       </c>
       <c r="K48" s="261">
-        <f>J48*SQRT(SUMSQ(Constants!$B$26/Constants!$B$25,CF!F48/CF!E48,Concentrations!J46/Concentrations!I46))</f>
-        <v>3.7567723264912817E-3</v>
+        <f>J48*SQRT((F48/E48)^2+(1-(E48-E50)/(E48))*(Concentrations!J46/Concentrations!I46)^2)</f>
+        <v>3.5972397183074828E-3</v>
       </c>
       <c r="L48" s="125"/>
       <c r="M48" s="24"/>
@@ -44622,7 +44625,7 @@
       </c>
       <c r="Q48" s="152">
         <f t="shared" ref="Q48" si="73">P48*SQRT(SUMSQ(K48/J48,O48/N48))</f>
-        <v>1.1907515845483049E-2</v>
+        <v>1.1434522371861431E-2</v>
       </c>
       <c r="R48" s="190"/>
       <c r="S48" s="24"/>
@@ -44687,7 +44690,7 @@
       <c r="H49" s="24"/>
       <c r="I49" s="24"/>
       <c r="J49" s="152"/>
-      <c r="K49" s="152"/>
+      <c r="K49" s="261"/>
       <c r="L49" s="120">
         <f>Masses!E50</f>
         <v>0.32641815239999999</v>
@@ -44739,8 +44742,8 @@
         <v>8.1988843389475208E-2</v>
       </c>
       <c r="K50" s="261">
-        <f>J50*SQRT(SUMSQ(Constants!$B$26/Constants!$B$25,CF!F50/CF!E50,Concentrations!J48/Concentrations!I48))</f>
-        <v>3.3200209880118311E-3</v>
+        <f>J50*SQRT((F50/E50)^2+(1-(E50-E52)/(E50))*(Concentrations!J48/Concentrations!I48)^2)</f>
+        <v>3.1644450374033956E-3</v>
       </c>
       <c r="L50" s="125"/>
       <c r="N50" s="24">
@@ -44757,7 +44760,7 @@
       </c>
       <c r="Q50" s="152">
         <f t="shared" ref="Q50" si="83">P50*SQRT(SUMSQ(K50/J50,O50/N50))</f>
-        <v>1.0380070324507764E-2</v>
+        <v>9.9228283497337193E-3</v>
       </c>
       <c r="T50" s="24">
         <f t="shared" ref="T50" si="84">J50*10000</f>
@@ -44802,7 +44805,7 @@
       <c r="H51" s="24"/>
       <c r="I51" s="24"/>
       <c r="J51" s="152"/>
-      <c r="K51" s="152"/>
+      <c r="K51" s="261"/>
       <c r="L51" s="120">
         <f>Masses!E52</f>
         <v>0.3328866929</v>
@@ -44854,8 +44857,8 @@
         <v>6.2815144843809692E-2</v>
       </c>
       <c r="K52" s="261">
-        <f>J52*SQRT(SUMSQ(Constants!$B$26/Constants!$B$25,CF!F52/CF!E52,Concentrations!J50/Concentrations!I50))</f>
-        <v>2.5331697340800884E-3</v>
+        <f>J52*SQRT((F52/E52)^2+(1-(E52-E54)/(E52))*(Concentrations!J50/Concentrations!I50)^2)</f>
+        <v>2.4096888064926484E-3</v>
       </c>
       <c r="L52" s="125"/>
       <c r="N52" s="24">
@@ -44872,7 +44875,7 @@
       </c>
       <c r="Q52" s="152">
         <f t="shared" ref="Q52" si="93">P52*SQRT(SUMSQ(K52/J52,O52/N52))</f>
-        <v>7.8548349986015103E-3</v>
+        <v>7.4940251418808747E-3</v>
       </c>
       <c r="T52" s="24">
         <f t="shared" ref="T52" si="94">J52*10000</f>
@@ -44917,7 +44920,7 @@
       <c r="H53" s="24"/>
       <c r="I53" s="24"/>
       <c r="J53" s="152"/>
-      <c r="K53" s="152"/>
+      <c r="K53" s="261"/>
       <c r="L53" s="120">
         <f>Masses!E54</f>
         <v>0.33107307899999999</v>
@@ -44969,8 +44972,8 @@
         <v>5.5079902332178507E-2</v>
       </c>
       <c r="K54" s="261">
-        <f>J54*SQRT(SUMSQ(Constants!$B$26/Constants!$B$25,CF!F54/CF!E54,Concentrations!J52/Concentrations!I52))</f>
-        <v>2.5100444745938936E-3</v>
+        <f>J54*SQRT((F54/E54)^2+(1-(E54-E56)/(E54))*(Concentrations!J52/Concentrations!I52)^2)</f>
+        <v>2.4195031337040794E-3</v>
       </c>
       <c r="L54" s="125"/>
       <c r="N54" s="24">
@@ -44987,7 +44990,7 @@
       </c>
       <c r="Q54" s="152">
         <f t="shared" ref="Q54" si="103">P54*SQRT(SUMSQ(K54/J54,O54/N54))</f>
-        <v>8.1288884959566307E-3</v>
+        <v>7.8499731029241428E-3</v>
       </c>
       <c r="T54" s="24">
         <f t="shared" ref="T54" si="104">J54*10000</f>
@@ -45032,7 +45035,7 @@
       <c r="H55" s="24"/>
       <c r="I55" s="24"/>
       <c r="J55" s="152"/>
-      <c r="K55" s="152"/>
+      <c r="K55" s="261"/>
       <c r="L55" s="120">
         <f>Masses!E56</f>
         <v>0.3018454793</v>
@@ -45084,8 +45087,8 @@
         <v>5.5443807629744171E-2</v>
       </c>
       <c r="K56" s="261">
-        <f>J56*SQRT(SUMSQ(Constants!$B$26/Constants!$B$25,CF!F56/CF!E56,Concentrations!J54/Concentrations!I54))</f>
-        <v>2.9243156766385024E-3</v>
+        <f>J56*SQRT((F56/E56)^2+(1-(E56-E58)/(E56))*(Concentrations!J54/Concentrations!I54)^2)</f>
+        <v>2.8036650961114707E-3</v>
       </c>
       <c r="L56" s="125"/>
       <c r="N56" s="24">
@@ -45102,7 +45105,7 @@
       </c>
       <c r="Q56" s="152">
         <f t="shared" ref="Q56" si="113">P56*SQRT(SUMSQ(K56/J56,O56/N56))</f>
-        <v>9.7013768005786219E-3</v>
+        <v>9.3173154897027034E-3</v>
       </c>
       <c r="T56" s="24">
         <f t="shared" ref="T56" si="114">J56*10000</f>
@@ -45147,7 +45150,7 @@
       <c r="H57" s="24"/>
       <c r="I57" s="24"/>
       <c r="J57" s="152"/>
-      <c r="K57" s="152"/>
+      <c r="K57" s="261"/>
       <c r="L57" s="120">
         <f>Masses!E58</f>
         <v>0.31333829670000002</v>
@@ -45199,8 +45202,8 @@
         <v>4.6981830654250926E-2</v>
       </c>
       <c r="K58" s="261">
-        <f>J58*SQRT(SUMSQ(Constants!$B$26/Constants!$B$25,CF!F58/CF!E58,Concentrations!J56/Concentrations!I56))</f>
-        <v>2.7766041626667991E-3</v>
+        <f>J58*SQRT((F58/E58)^2+(1-(E58-E60)/(E58))*(Concentrations!J56/Concentrations!I56)^2)</f>
+        <v>2.6708633874606208E-3</v>
       </c>
       <c r="L58" s="125"/>
       <c r="N58" s="24">
@@ -45217,7 +45220,7 @@
       </c>
       <c r="Q58" s="152">
         <f t="shared" ref="Q58" si="123">P58*SQRT(SUMSQ(K58/J58,O58/N58))</f>
-        <v>9.2023777552201654E-3</v>
+        <v>8.8641112555119216E-3</v>
       </c>
       <c r="R58" s="43"/>
       <c r="T58" s="24">
@@ -45263,7 +45266,7 @@
       <c r="H59" s="24"/>
       <c r="I59" s="24"/>
       <c r="J59" s="152"/>
-      <c r="K59" s="152"/>
+      <c r="K59" s="261"/>
       <c r="L59" s="120">
         <f>Masses!E60</f>
         <v>0.30068124229999998</v>
@@ -45315,8 +45318,8 @@
         <v>3.9304467168636351E-2</v>
       </c>
       <c r="K60" s="261">
-        <f>J60*SQRT(SUMSQ(Constants!$B$26/Constants!$B$25,CF!F60/CF!E60,Concentrations!J58/Concentrations!I58))</f>
-        <v>2.6887855698727887E-3</v>
+        <f>J60*SQRT((F60/E60)^2+(1-(E60-E62)/(E60))*(Concentrations!J58/Concentrations!I58)^2)</f>
+        <v>2.5897970685396922E-3</v>
       </c>
       <c r="L60" s="125"/>
       <c r="N60" s="24">
@@ -45333,7 +45336,7 @@
       </c>
       <c r="Q60" s="152">
         <f t="shared" ref="Q60" si="133">P60*SQRT(SUMSQ(K60/J60,O60/N60))</f>
-        <v>8.9082175813352763E-3</v>
+        <v>8.5897277652927408E-3</v>
       </c>
       <c r="T60" s="24">
         <f t="shared" ref="T60" si="134">J60*10000</f>
@@ -45378,7 +45381,7 @@
       <c r="H61" s="24"/>
       <c r="I61" s="24"/>
       <c r="J61" s="152"/>
-      <c r="K61" s="152"/>
+      <c r="K61" s="261"/>
       <c r="L61" s="120">
         <f>Masses!E62</f>
         <v>0.3117251707</v>
@@ -45430,8 +45433,8 @@
         <v>3.7151849630752874E-2</v>
       </c>
       <c r="K62" s="261">
-        <f>J62*SQRT(SUMSQ(Constants!$B$26/Constants!$B$25,CF!F62/CF!E62,Concentrations!J60/Concentrations!I60))</f>
-        <v>3.233624076234259E-3</v>
+        <f>J62*SQRT((F62/E62)^2+(1-(E62-E64)/(E62))*(Concentrations!J60/Concentrations!I60)^2)</f>
+        <v>3.141473662355931E-3</v>
       </c>
       <c r="L62" s="125"/>
       <c r="N62" s="24">
@@ -45448,7 +45451,7 @@
       </c>
       <c r="Q62" s="152">
         <f t="shared" ref="Q62" si="143">P62*SQRT(SUMSQ(K62/J62,O62/N62))</f>
-        <v>1.0609184771879172E-2</v>
+        <v>1.031248458565074E-2</v>
       </c>
       <c r="T62" s="24">
         <f t="shared" ref="T62" si="144">J62*10000</f>
@@ -45493,7 +45496,7 @@
       <c r="H63" s="24"/>
       <c r="I63" s="24"/>
       <c r="J63" s="152"/>
-      <c r="K63" s="152"/>
+      <c r="K63" s="261"/>
       <c r="L63" s="120">
         <f>Masses!E64</f>
         <v>0.30354376399999999</v>
@@ -45560,8 +45563,8 @@
         <v>4.0200029733103541E-2</v>
       </c>
       <c r="K64" s="261">
-        <f>J64*SQRT(SUMSQ(Constants!$B$26/Constants!$B$25,CF!F64/CF!E64,Concentrations!J62/Concentrations!I62))</f>
-        <v>4.3879288069944497E-3</v>
+        <f>J64*SQRT((F64/E64)^2+(1-(E64-E66)/(E64))*(Concentrations!J62/Concentrations!I62)^2)</f>
+        <v>4.2196475228406293E-3</v>
       </c>
       <c r="L64" s="125"/>
       <c r="N64" s="24">
@@ -45578,7 +45581,7 @@
       </c>
       <c r="Q64" s="152">
         <f t="shared" ref="Q64" si="153">P64*SQRT(SUMSQ(K64/J64,O64/N64))</f>
-        <v>1.3994881325316568E-2</v>
+        <v>1.3464051124115278E-2</v>
       </c>
       <c r="T64" s="24">
         <f t="shared" ref="T64" si="154">J64*10000</f>
@@ -45638,7 +45641,7 @@
       <c r="H65" s="24"/>
       <c r="I65" s="24"/>
       <c r="J65" s="152"/>
-      <c r="K65" s="152"/>
+      <c r="K65" s="261"/>
       <c r="L65" s="120">
         <f>Masses!E66</f>
         <v>0.3269324542</v>
@@ -45707,8 +45710,8 @@
         <v>3.3888064195329019E-2</v>
       </c>
       <c r="K66" s="261">
-        <f>J66*SQRT(SUMSQ(Constants!$B$26/Constants!$B$25,CF!F66/CF!E66,Concentrations!J64/Concentrations!I64))</f>
-        <v>4.5337426303250035E-3</v>
+        <f>J66*SQRT((F66/E66)^2+(1-(E66-E68)/(E66))*(Concentrations!J64/Concentrations!I64)^2)</f>
+        <v>4.3620107777435912E-3</v>
       </c>
       <c r="L66" s="125"/>
       <c r="N66" s="24">
@@ -45725,7 +45728,7 @@
       </c>
       <c r="Q66" s="152">
         <f t="shared" ref="Q66" si="163">P66*SQRT(SUMSQ(K66/J66,O66/N66))</f>
-        <v>1.381275821925522E-2</v>
+        <v>1.3293029165772073E-2</v>
       </c>
       <c r="T66" s="24">
         <f t="shared" ref="T66" si="164">J66*10000</f>
@@ -45785,7 +45788,7 @@
       <c r="H67" s="24"/>
       <c r="I67" s="24"/>
       <c r="J67" s="152"/>
-      <c r="K67" s="152"/>
+      <c r="K67" s="261"/>
       <c r="L67" s="120">
         <f>Masses!E68</f>
         <v>0.33167596739999999</v>
@@ -45857,8 +45860,8 @@
         <v>3.0623321362616682E-2</v>
       </c>
       <c r="K68" s="261">
-        <f>J68*SQRT(SUMSQ(Constants!$B$26/Constants!$B$25,CF!F68/CF!E68,Concentrations!J66/Concentrations!I66))</f>
-        <v>5.5090022774232587E-3</v>
+        <f>J68*SQRT((F68/E68)^2+(1-(E68-E70)/(E68))*(Concentrations!J66/Concentrations!I66)^2)</f>
+        <v>5.3569017718802965E-3</v>
       </c>
       <c r="L68" s="125"/>
       <c r="N68" s="24">
@@ -45875,7 +45878,7 @@
       </c>
       <c r="Q68" s="152">
         <f t="shared" ref="Q68" si="173">P68*SQRT(SUMSQ(K68/J68,O68/N68))</f>
-        <v>1.7439281196593322E-2</v>
+        <v>1.6959698059579715E-2</v>
       </c>
       <c r="T68" s="24">
         <f t="shared" ref="T68" si="174">J68*10000</f>
@@ -45941,7 +45944,7 @@
       <c r="H69" s="24"/>
       <c r="I69" s="24"/>
       <c r="J69" s="152"/>
-      <c r="K69" s="152"/>
+      <c r="K69" s="261"/>
       <c r="L69" s="120">
         <f>Masses!E70</f>
         <v>0.30135291780000001</v>
@@ -46015,8 +46018,8 @@
         <v>3.2264826076202589E-2</v>
       </c>
       <c r="K70" s="261">
-        <f>J70*SQRT(SUMSQ(Constants!$B$26/Constants!$B$25,CF!F70/CF!E70,Concentrations!J68/Concentrations!I68))</f>
-        <v>7.5543728930421578E-3</v>
+        <f>J70*SQRT((F70/E70)^2+(1-(E70-E72)/(E70))*(Concentrations!J68/Concentrations!I68)^2)</f>
+        <v>7.2875034732795274E-3</v>
       </c>
       <c r="L70" s="125"/>
       <c r="N70" s="24">
@@ -46033,7 +46036,7 @@
       </c>
       <c r="Q70" s="152">
         <f t="shared" ref="Q70" si="182">P70*SQRT(SUMSQ(K70/J70,O70/N70))</f>
-        <v>2.4974386296262419E-2</v>
+        <v>2.4094413627352648E-2</v>
       </c>
       <c r="T70" s="24">
         <f t="shared" ref="T70" si="183">J70*10000</f>
@@ -46095,7 +46098,7 @@
       <c r="H71" s="24"/>
       <c r="I71" s="24"/>
       <c r="J71" s="152"/>
-      <c r="K71" s="152"/>
+      <c r="K71" s="261"/>
       <c r="L71" s="120">
         <f>Masses!E72</f>
         <v>0.30438742089999998</v>
@@ -46168,8 +46171,8 @@
         <v>3.1624949244065892E-2</v>
       </c>
       <c r="K72" s="261">
-        <f>J72*SQRT(SUMSQ(Constants!$B$26/Constants!$B$25,CF!F72/CF!E72,Concentrations!J70/Concentrations!I70))</f>
-        <v>9.8837849729342293E-3</v>
+        <f>J72*SQRT((F72/E72)^2+(1-(E72-E74)/(E72))*(Concentrations!J70/Concentrations!I70)^2)</f>
+        <v>9.599233867156453E-3</v>
       </c>
       <c r="L72" s="125"/>
       <c r="N72" s="24">
@@ -46186,7 +46189,7 @@
       </c>
       <c r="Q72" s="152">
         <f t="shared" ref="Q72" si="191">P72*SQRT(SUMSQ(K72/J72,O72/N72))</f>
-        <v>3.3119007610806273E-2</v>
+        <v>3.2167017120461876E-2</v>
       </c>
       <c r="T72" s="24">
         <f t="shared" ref="T72" si="192">J72*10000</f>
@@ -46246,7 +46249,7 @@
       <c r="H73" s="24"/>
       <c r="I73" s="24"/>
       <c r="J73" s="152"/>
-      <c r="K73" s="152"/>
+      <c r="K73" s="261"/>
       <c r="L73" s="120">
         <f>Masses!E74</f>
         <v>0.29293916120000002</v>
@@ -46314,8 +46317,8 @@
         <v>3.7583425947905064E-2</v>
       </c>
       <c r="K74" s="261">
-        <f>J74*SQRT(SUMSQ(Constants!$B$26/Constants!$B$25,CF!F74/CF!E74,Concentrations!J72/Concentrations!I72))</f>
-        <v>1.5506428790236603E-2</v>
+        <f>J74*SQRT((F74/E74)^2+(1-(E74-E76)/(E74))*(Concentrations!J72/Concentrations!I72)^2)</f>
+        <v>1.4928059559805673E-2</v>
       </c>
       <c r="L74" s="125"/>
       <c r="N74" s="24">
@@ -46332,7 +46335,7 @@
       </c>
       <c r="Q74" s="152">
         <f t="shared" ref="Q74" si="200">P74*SQRT(SUMSQ(K74/J74,O74/N74))</f>
-        <v>5.2015502008105501E-2</v>
+        <v>5.0077185236543149E-2</v>
       </c>
       <c r="T74" s="24">
         <f t="shared" ref="T74" si="201">J74*10000</f>
@@ -48693,26 +48696,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f41172b4-acf7-42f8-9b6d-390c68595efb">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="7a8db90d-979a-496b-a33a-0e81ef58e38d" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009CF9DB384D2B9B4F909E7CE6390FD386" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2a4a7879e4345142aa631bf45f8a5b53">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f41172b4-acf7-42f8-9b6d-390c68595efb" xmlns:ns3="7a8db90d-979a-496b-a33a-0e81ef58e38d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3a4db3941a01b7f82d6d75b66ed506e6" ns2:_="" ns3:_="">
     <xsd:import namespace="f41172b4-acf7-42f8-9b6d-390c68595efb"/>
@@ -48967,26 +48950,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2618D8D-E1C2-4A32-A721-61926D6C9208}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="f41172b4-acf7-42f8-9b6d-390c68595efb"/>
-    <ds:schemaRef ds:uri="7a8db90d-979a-496b-a33a-0e81ef58e38d"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB701B81-DB63-4E41-8428-7D2C1AC9C10B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f41172b4-acf7-42f8-9b6d-390c68595efb">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="7a8db90d-979a-496b-a33a-0e81ef58e38d" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4609FFB3-B224-40E1-BD93-DC7F76936FB5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -49003,4 +48987,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB701B81-DB63-4E41-8428-7D2C1AC9C10B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2618D8D-E1C2-4A32-A721-61926D6C9208}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="f41172b4-acf7-42f8-9b6d-390c68595efb"/>
+    <ds:schemaRef ds:uri="7a8db90d-979a-496b-a33a-0e81ef58e38d"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>